--- a/docs/엔진/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\docs\엔진\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5524A74-BAE0-4D8B-87BC-33DF7B5882FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146FE2CE-1249-4BB2-99F9-5D8565C7B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42240" yWindow="2460" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15315,7 +15315,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -15385,6 +15385,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -15443,7 +15456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -15529,7 +15542,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19722,16 +19744,16 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="52">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="36" t="s">
         <v>5073</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="36" t="s">
         <v>5074</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="36" t="s">
         <v>5075</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="36" t="s">
         <v>5076</v>
       </c>
     </row>
@@ -23727,13 +23749,13 @@
       <c r="C64" s="6" t="s">
         <v>1658</v>
       </c>
-      <c r="D64" s="33" t="s">
+      <c r="D64" s="34" t="s">
         <v>5070</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>1433</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="35">
         <v>365</v>
       </c>
       <c r="G64" s="6" t="s">
@@ -23743,7 +23765,7 @@
       <c r="I64" s="6" t="s">
         <v>1419</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" s="33" t="s">
         <v>5071</v>
       </c>
       <c r="K64" s="6">
@@ -24989,7 +25011,7 @@
       <c r="C22" s="6" t="s">
         <v>1764</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="35">
         <v>365</v>
       </c>
       <c r="E22" s="5"/>
@@ -24999,7 +25021,7 @@
       <c r="G22" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="33" t="s">
         <v>5072</v>
       </c>
     </row>
@@ -33447,10 +33469,10 @@
       <c r="B45" s="6" t="s">
         <v>2369</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="33" t="s">
         <v>5068</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="33" t="s">
         <v>5069</v>
       </c>
     </row>
@@ -79698,7 +79720,7 @@
         <v>5045</v>
       </c>
       <c r="G450" s="24">
-        <f t="shared" ref="G450:G513" si="14">LEN(F450)</f>
+        <f t="shared" ref="G450:G467" si="14">LEN(F450)</f>
         <v>24</v>
       </c>
       <c r="H450" s="24">
@@ -79708,7 +79730,7 @@
         <v>64</v>
       </c>
       <c r="J450" s="24" t="str">
-        <f t="shared" ref="J450:J513" si="15">IF(F450="","비어 있음",IF(G450&lt;=H450,"OK",IF(G450&lt;=I450,"길이 주의","상한 초과")))</f>
+        <f t="shared" ref="J450:J467" si="15">IF(F450="","비어 있음",IF(G450&lt;=H450,"OK",IF(G450&lt;=I450,"길이 주의","상한 초과")))</f>
         <v>OK</v>
       </c>
       <c r="K450" s="24" t="s">

--- a/docs/엔진/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\docs\엔진\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A17E3E-6C98-495B-9A33-54217D159923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB483C7F-AECA-4125-8109-80411EC83648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16156" uniqueCount="5077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16172" uniqueCount="5081">
   <si>
     <t>항목</t>
   </si>
@@ -15305,7 +15305,83 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. · 최근 것이 위</t>
+    <t>상태</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>전달</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반영</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+  </si>
+  <si>
+    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. · 최근 것이 위 · 반영 완료 9건은 맨 아래에 숨김(행 번호 사이를 우클릭 → 숨기기 취소)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -15316,7 +15392,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -15399,8 +15475,47 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15425,6 +15540,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF17324D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -15457,7 +15590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -15554,6 +15687,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -19353,12 +19495,12 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="43.58203125" customWidth="1"/>
     <col min="2" max="4" width="60.58203125" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -19520,15 +19662,15 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>5076</v>
+        <v>5080</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
         <v>0</v>
       </c>
@@ -19541,8 +19683,11 @@
       <c r="D19" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="52">
+      <c r="E19" s="5" t="s">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="52">
       <c r="A20" s="36" t="s">
         <v>5072</v>
       </c>
@@ -19555,148 +19700,181 @@
       <c r="D20" s="36" t="s">
         <v>5075</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="52">
+      <c r="E20" s="37" t="s">
+        <v>5077</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="39">
       <c r="A21" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="52">
+      <c r="A22" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="52">
+      <c r="A23" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="52">
+      <c r="A24" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="65" customHeight="1">
+      <c r="A25" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="52" hidden="1">
+      <c r="A26" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B26" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C26" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D26" s="32" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="65">
-      <c r="A22" s="32" t="s">
+      <c r="E26" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="65" hidden="1">
+      <c r="A27" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B27" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C27" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D27" s="32" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="39">
-      <c r="A23" s="32" t="s">
+      <c r="E27" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="39" hidden="1">
+      <c r="A28" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B28" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C28" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D28" s="32" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="78">
-      <c r="A24" s="32" t="s">
+      <c r="E28" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="78" hidden="1">
+      <c r="A29" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B29" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D29" s="32" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="182">
-      <c r="A25" s="32" t="s">
+      <c r="E29" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="182" hidden="1">
+      <c r="A30" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B30" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C30" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D30" s="32" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="39">
-      <c r="A26" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="52">
-      <c r="A27" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="52">
-      <c r="A28" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="52">
-      <c r="A29" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="65" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="65" customHeight="1">
+      <c r="E30" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="65" hidden="1" customHeight="1">
       <c r="A31" s="32" t="s">
         <v>45</v>
       </c>
@@ -19709,8 +19887,11 @@
       <c r="D31" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="39" customHeight="1">
+      <c r="E31" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A32" s="32" t="s">
         <v>41</v>
       </c>
@@ -19723,8 +19904,11 @@
       <c r="D32" s="32" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="52" customHeight="1">
+      <c r="E32" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="52" hidden="1" customHeight="1">
       <c r="A33" s="32" t="s">
         <v>37</v>
       </c>
@@ -19737,8 +19921,11 @@
       <c r="D33" s="32" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="52" customHeight="1">
+      <c r="E33" s="39" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="52" hidden="1" customHeight="1">
       <c r="A34" s="32" t="s">
         <v>33</v>
       </c>
@@ -19750,6 +19937,9 @@
       </c>
       <c r="D34" s="32" t="s">
         <v>36</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>5079</v>
       </c>
     </row>
   </sheetData>
